--- a/data/players/Connor_Taylor_master.xlsx
+++ b/data/players/Connor_Taylor_master.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Physical" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Pressing" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Off_Ball_Runs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Match_by_Match" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Wyscout" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Merged" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physical" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pressing" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off_Ball_Runs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Match_by_Match" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wyscout" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Merged" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -60,11 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -763,17 +767,12 @@
       <c r="AH2" t="n">
         <v>1.09</v>
       </c>
-      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
         <v>14</v>
       </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -913,7 +912,6 @@
       <c r="AM3" t="n">
         <v>10</v>
       </c>
-      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
         <v>3.49</v>
       </c>
@@ -1041,17 +1039,12 @@
       <c r="AH4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
         <v>15</v>
       </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1176,17 +1169,12 @@
       <c r="AH5" t="n">
         <v>1.29</v>
       </c>
-      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
         <v>15</v>
       </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1311,21 +1299,18 @@
       <c r="AH6" t="n">
         <v>0.71</v>
       </c>
-      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
         <v>3</v>
       </c>
       <c r="AK6" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="n">
         <v>21</v>
       </c>
       <c r="AN6" t="n">
         <v>2.15</v>
       </c>
-      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1447,17 +1432,12 @@
       <c r="AG7" t="n">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="n">
         <v>13</v>
       </c>
-      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
         <v>3.06</v>
       </c>
@@ -1585,18 +1565,15 @@
       <c r="AH8" t="n">
         <v>0.96</v>
       </c>
-      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="n">
         <v>3</v>
       </c>
       <c r="AK8" t="n">
         <v>1.88</v>
       </c>
-      <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="n">
         <v>20</v>
       </c>
-      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
         <v>3.03</v>
       </c>
@@ -1721,18 +1698,12 @@
       <c r="AG9" t="n">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="n">
         <v>16</v>
       </c>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1863,15 +1834,12 @@
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="n">
         <v>18</v>
       </c>
       <c r="AN10" t="n">
         <v>2.38</v>
       </c>
-      <c r="AO10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2002,13 +1970,9 @@
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="n">
         <v>11</v>
       </c>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2130,18 +2094,12 @@
       <c r="AG12" t="n">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="n">
         <v>7</v>
       </c>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2408,17 +2366,12 @@
       <c r="AG14" t="n">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="n">
         <v>4</v>
       </c>
-      <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="n">
         <v>3.23</v>
       </c>
@@ -2543,20 +2496,15 @@
       <c r="AG15" t="n">
         <v>0</v>
       </c>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="n">
         <v>11</v>
       </c>
       <c r="AN15" t="n">
         <v>2.83</v>
       </c>
-      <c r="AO15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2660,7 +2608,6 @@
       <c r="AA16" t="n">
         <v>2</v>
       </c>
-      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
         <v>8</v>
       </c>
@@ -2676,18 +2623,12 @@
       <c r="AG16" t="n">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="n">
         <v>1</v>
       </c>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2809,18 +2750,12 @@
       <c r="AG17" t="n">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="n">
         <v>6</v>
       </c>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2942,17 +2877,12 @@
       <c r="AG18" t="n">
         <v>0</v>
       </c>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="n">
         <v>7</v>
       </c>
-      <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="n">
         <v>3.52</v>
       </c>
@@ -3077,18 +3007,12 @@
       <c r="AG19" t="n">
         <v>0</v>
       </c>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="n">
         <v>4</v>
       </c>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3210,18 +3134,12 @@
       <c r="AG20" t="n">
         <v>0</v>
       </c>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="n">
         <v>1</v>
       </c>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3346,18 +3264,15 @@
       <c r="AH21" t="n">
         <v>0.9</v>
       </c>
-      <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="n">
         <v>1</v>
       </c>
       <c r="AK21" t="n">
         <v>1.87</v>
       </c>
-      <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="n">
         <v>1</v>
       </c>
-      <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="n">
         <v>3.28</v>
       </c>
@@ -3485,17 +3400,12 @@
       <c r="AH22" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="n">
         <v>0</v>
       </c>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="n">
         <v>7</v>
       </c>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3626,13 +3536,9 @@
       <c r="AJ23" t="n">
         <v>0</v>
       </c>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="n">
         <v>18</v>
       </c>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3757,21 +3663,18 @@
       <c r="AH24" t="n">
         <v>0.83</v>
       </c>
-      <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="n">
         <v>4</v>
       </c>
       <c r="AK24" t="n">
         <v>1.6</v>
       </c>
-      <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="n">
         <v>18</v>
       </c>
       <c r="AN24" t="n">
         <v>2.21</v>
       </c>
-      <c r="AO24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4102,7 +4005,6 @@
       <c r="AG2" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
         <v>3</v>
       </c>
@@ -4241,7 +4143,6 @@
       <c r="AG3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
         <v>5</v>
       </c>
@@ -4380,14 +4281,12 @@
       <c r="AG4" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
-      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4517,14 +4416,12 @@
       <c r="AG5" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
-      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4654,7 +4551,6 @@
       <c r="AG6" t="n">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
         <v>1</v>
       </c>
@@ -4793,14 +4689,12 @@
       <c r="AG7" t="n">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
-      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4930,7 +4824,6 @@
       <c r="AG8" t="n">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
@@ -5069,7 +4962,6 @@
       <c r="AG9" t="n">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
         <v>2</v>
       </c>
@@ -5208,7 +5100,6 @@
       <c r="AG10" t="n">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
         <v>2</v>
       </c>
@@ -5347,7 +5238,6 @@
       <c r="AG11" t="n">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
         <v>4</v>
       </c>
@@ -5468,8 +5358,6 @@
       <c r="AA12" t="n">
         <v>0</v>
       </c>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
@@ -5482,14 +5370,12 @@
       <c r="AG12" t="n">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
-      <c r="AK12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5619,7 +5505,6 @@
       <c r="AG13" t="n">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
         <v>3</v>
       </c>
@@ -5758,7 +5643,6 @@
       <c r="AG14" t="n">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
         <v>4</v>
       </c>
@@ -5897,14 +5781,12 @@
       <c r="AG15" t="n">
         <v>0</v>
       </c>
-      <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
-      <c r="AK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6034,7 +5916,6 @@
       <c r="AG16" t="n">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
         <v>3</v>
       </c>
@@ -6173,7 +6054,6 @@
       <c r="AG17" t="n">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
         <v>1</v>
       </c>
@@ -6312,7 +6192,6 @@
       <c r="AG18" t="n">
         <v>0</v>
       </c>
-      <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
         <v>4</v>
       </c>
@@ -6451,14 +6330,12 @@
       <c r="AG19" t="n">
         <v>0</v>
       </c>
-      <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
-      <c r="AK19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6588,14 +6465,12 @@
       <c r="AG20" t="n">
         <v>0</v>
       </c>
-      <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
-      <c r="AK20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6725,7 +6600,6 @@
       <c r="AG21" t="n">
         <v>0</v>
       </c>
-      <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
         <v>1</v>
       </c>
@@ -9908,18 +9782,12 @@
       <c r="AA2" t="n">
         <v>1</v>
       </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
         <v>14</v>
       </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10011,18 +9879,12 @@
       <c r="AA3" t="n">
         <v>1</v>
       </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
         <v>1</v>
       </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
         <v>10</v>
       </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10114,18 +9976,12 @@
       <c r="AA4" t="n">
         <v>2</v>
       </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
         <v>15</v>
       </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10217,18 +10073,12 @@
       <c r="AA5" t="n">
         <v>3</v>
       </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
         <v>15</v>
       </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10320,18 +10170,12 @@
       <c r="AA6" t="n">
         <v>6</v>
       </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
         <v>3</v>
       </c>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
         <v>21</v>
       </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10423,18 +10267,12 @@
       <c r="AA7" t="n">
         <v>0</v>
       </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
         <v>13</v>
       </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10526,18 +10364,12 @@
       <c r="AA8" t="n">
         <v>6</v>
       </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="n">
         <v>3</v>
       </c>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="n">
         <v>20</v>
       </c>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10629,18 +10461,12 @@
       <c r="AA9" t="n">
         <v>0</v>
       </c>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
         <v>16</v>
       </c>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10732,18 +10558,12 @@
       <c r="AA10" t="n">
         <v>6</v>
       </c>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
         <v>18</v>
       </c>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10835,18 +10655,12 @@
       <c r="AA11" t="n">
         <v>2</v>
       </c>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="n">
         <v>11</v>
       </c>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10938,18 +10752,12 @@
       <c r="AA12" t="n">
         <v>0</v>
       </c>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="n">
         <v>7</v>
       </c>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11041,18 +10849,12 @@
       <c r="AA13" t="n">
         <v>3</v>
       </c>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="n">
         <v>1</v>
       </c>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="n">
         <v>21</v>
       </c>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11144,18 +10946,12 @@
       <c r="AA14" t="n">
         <v>0</v>
       </c>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="n">
         <v>4</v>
       </c>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11190,37 +10986,12 @@
       <c r="H15" t="n">
         <v>1211</v>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11312,18 +11083,12 @@
       <c r="AA16" t="n">
         <v>0</v>
       </c>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="n">
         <v>11</v>
       </c>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11394,8 +11159,6 @@
       <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
       <c r="W17" t="n">
         <v>8</v>
       </c>
@@ -11411,18 +11174,12 @@
       <c r="AA17" t="n">
         <v>0</v>
       </c>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="n">
         <v>1</v>
       </c>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11514,18 +11271,12 @@
       <c r="AA18" t="n">
         <v>0</v>
       </c>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="n">
         <v>0</v>
       </c>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="n">
         <v>6</v>
       </c>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11617,18 +11368,12 @@
       <c r="AA19" t="n">
         <v>0</v>
       </c>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="n">
         <v>0</v>
       </c>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="n">
         <v>7</v>
       </c>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11720,18 +11465,12 @@
       <c r="AA20" t="n">
         <v>0</v>
       </c>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="n">
         <v>0</v>
       </c>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="n">
         <v>4</v>
       </c>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11823,18 +11562,12 @@
       <c r="AA21" t="n">
         <v>0</v>
       </c>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="n">
         <v>0</v>
       </c>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
         <v>1</v>
       </c>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11926,18 +11659,12 @@
       <c r="AA22" t="n">
         <v>1</v>
       </c>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="n">
         <v>1</v>
       </c>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="n">
         <v>1</v>
       </c>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12029,18 +11756,12 @@
       <c r="AA23" t="n">
         <v>3</v>
       </c>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="n">
         <v>0</v>
       </c>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="n">
         <v>7</v>
       </c>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12132,18 +11853,12 @@
       <c r="AA24" t="n">
         <v>2</v>
       </c>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="n">
         <v>0</v>
       </c>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="n">
         <v>18</v>
       </c>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12235,18 +11950,12 @@
       <c r="AA25" t="n">
         <v>4</v>
       </c>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="n">
         <v>4</v>
       </c>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="n">
         <v>18</v>
       </c>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12259,366 +11968,366 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT24"/>
+  <dimension ref="A1:BT28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Match</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Minutes played</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total actions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>successful</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Goals</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Assists</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Shots</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>on target</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>xG</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Passes</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>accurate</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Long passes</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>accurate</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>accurate.1</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Crosses</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>accurate</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>accurate.2</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>Dribbles</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>successful</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>successful.1</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>Duels</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>won</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Aerial duels</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>won</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>won.1</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Interceptions</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>own half</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Recoveries</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>opp. half</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Yellow card</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Red card</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Defensive duels</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>won</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>won.2</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Loose ball duels</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>won</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>won.3</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Sliding tackles</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>successful</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>successful.2</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Clearances</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Fouls</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Yellow cards</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Red cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Shot assists</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Offensive duels</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>won</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>won.4</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Touches in penalty area</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Offsides</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Progressive runs</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Fouls suffered</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Through passes</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>accurate</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>accurate.3</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
         <is>
           <t>xA</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Second assists</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>Passes to final third</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>accurate</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>accurate.4</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
         <is>
           <t>Passes to penalty area</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>accurate</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>accurate.5</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
         <is>
           <t>Received passes</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>Forward passes</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>accurate</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>accurate.6</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
         <is>
           <t>Back passes</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>accurate</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>accurate.7</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>Conceded goals</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>xCG</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>Shots against</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>Saves</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>with reflexes</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>Exits</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>Passes to GK</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>accurate</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>accurate.8</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
         <is>
           <t>Goal kicks</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>Short goal kicks</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>Long goal kicks</t>
         </is>
@@ -12627,7 +12336,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers - Wigan Athletic 2:0</t>
+          <t>Cardiff City - Wycombe Wanderers 0:2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -12635,214 +12344,178 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+      <c r="C2" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="F2" t="n">
+        <v>85</v>
+      </c>
+      <c r="G2" t="n">
+        <v>71</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="M2" t="n">
+        <v>68</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>6</v>
       </c>
-      <c r="G2" t="n">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA2" t="n">
         <v>5</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="AB2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
         <v>4</v>
       </c>
-      <c r="N2" t="n">
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS2" t="n">
         <v>4</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
       </c>
       <c r="BT2" t="n">
         <v>0</v>
@@ -12851,7 +12524,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Northampton Town - Wycombe Wanderers 1:2</t>
+          <t>Wycombe Wanderers - Luton Town 1:2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12859,120 +12532,102 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-01-17</t>
-        </is>
+      <c r="C3" s="2" t="n">
+        <v>46095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RCB</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
+        <v>61</v>
+      </c>
+      <c r="G3" t="n">
+        <v>42</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>34</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>17</v>
+      </c>
+      <c r="V3" t="n">
         <v>11</v>
       </c>
-      <c r="G3" t="n">
+      <c r="W3" t="n">
+        <v>7</v>
+      </c>
+      <c r="X3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB3" t="n">
         <v>9</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG3" t="n">
         <v>5</v>
       </c>
-      <c r="N3" t="n">
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="n">
         <v>5</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>4</v>
-      </c>
-      <c r="V3" t="n">
-        <v>4</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -12987,10 +12642,10 @@
         <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
@@ -12999,14 +12654,12 @@
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
@@ -13014,32 +12667,22 @@
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BF3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>3</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="n">
         <v>0</v>
       </c>
@@ -13049,26 +12692,18 @@
       <c r="BL3" t="n">
         <v>0</v>
       </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="n">
         <v>0</v>
       </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
       <c r="BR3" t="n">
         <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BT3" t="n">
         <v>0</v>
@@ -13077,7 +12712,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers - AFC Wimbledon 2:0</t>
+          <t>Bolton Wanderers - Wycombe Wanderers 3:2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -13085,24 +12720,22 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-01-04</t>
-        </is>
+      <c r="C4" s="2" t="n">
+        <v>46088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>CB, RCB</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -13120,83 +12753,67 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
         <v>11</v>
       </c>
-      <c r="N4" t="n">
+      <c r="V4" t="n">
+        <v>6</v>
+      </c>
+      <c r="W4" t="n">
         <v>8</v>
       </c>
-      <c r="O4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="X4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y4" t="n">
         <v>4</v>
       </c>
-      <c r="V4" t="n">
-        <v>2</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>7</v>
       </c>
-      <c r="Z4" t="n">
-        <v>8</v>
-      </c>
       <c r="AA4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="n">
         <v>5</v>
       </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>4</v>
-      </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
@@ -13210,7 +12827,7 @@
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -13230,9 +12847,7 @@
       <c r="AW4" t="n">
         <v>0</v>
       </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
@@ -13242,30 +12857,20 @@
       <c r="BA4" t="n">
         <v>1</v>
       </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
@@ -13275,21 +12880,13 @@
       <c r="BL4" t="n">
         <v>0</v>
       </c>
-      <c r="BM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="n">
         <v>0</v>
       </c>
-      <c r="BP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0</v>
-      </c>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
       <c r="BR4" t="n">
         <v>0</v>
       </c>
@@ -13303,7 +12900,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Plymouth Argyle - Wycombe Wanderers 1:1</t>
+          <t>Barnsley - Wycombe Wanderers 0:1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -13311,24 +12908,22 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
-        </is>
+      <c r="C5" s="2" t="n">
+        <v>46084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RCB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -13346,52 +12941,44 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -13403,25 +12990,17 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -13456,9 +13035,7 @@
       <c r="AW5" t="n">
         <v>0</v>
       </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
@@ -13468,30 +13045,20 @@
       <c r="BA5" t="n">
         <v>0</v>
       </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
+      <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="n">
         <v>0</v>
       </c>
@@ -13501,26 +13068,18 @@
       <c r="BL5" t="n">
         <v>0</v>
       </c>
-      <c r="BM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0</v>
-      </c>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="n">
         <v>0</v>
       </c>
-      <c r="BP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0</v>
-      </c>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
       <c r="BR5" t="n">
         <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
         <v>0</v>
@@ -13529,7 +13088,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers - Bolton Wanderers 2:1</t>
+          <t>Wycombe Wanderers - Wigan Athletic 2:0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -13537,49 +13096,47 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2025-12-20</t>
-        </is>
+      <c r="C6" s="2" t="n">
+        <v>46049</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -13594,28 +13151,28 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -13627,10 +13184,10 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -13645,7 +13202,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -13690,10 +13247,10 @@
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
@@ -13702,13 +13259,13 @@
         <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -13753,7 +13310,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers - Plymouth Argyle 0:1</t>
+          <t>Northampton Town - Wycombe Wanderers 1:2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -13761,24 +13318,22 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
+      <c r="C7" s="2" t="n">
+        <v>46039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RCB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -13787,25 +13342,25 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -13820,31 +13375,31 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="W7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AC7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -13853,16 +13408,16 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -13871,7 +13426,7 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -13889,16 +13444,16 @@
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
         <v>1</v>
@@ -13916,10 +13471,10 @@
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
@@ -13928,19 +13483,19 @@
         <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="BG7" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
         <v>0</v>
@@ -13961,10 +13516,10 @@
         <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
         <v>0</v>
@@ -13979,32 +13534,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Northampton Town - Wycombe Wanderers 2:0</t>
+          <t>Wycombe Wanderers - AFC Wimbledon 2:0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>England. EFL Vertu Trophy</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
+          <t>England. League One</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>46026</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CB, LCB, RCB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -14013,64 +13566,64 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="N8" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
         <v>4</v>
       </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>15</v>
-      </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
         <v>7</v>
       </c>
-      <c r="X8" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>6</v>
-      </c>
       <c r="Z8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA8" t="n">
         <v>6</v>
       </c>
       <c r="AB8" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -14079,26 +13632,26 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
         <v>4</v>
       </c>
-      <c r="AH8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>3</v>
-      </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
@@ -14115,10 +13668,10 @@
         <v>1</v>
       </c>
       <c r="AR8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT8" t="n">
         <v>0</v>
@@ -14127,7 +13680,7 @@
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -14142,7 +13695,7 @@
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB8" t="n">
         <v>0</v>
@@ -14151,22 +13704,22 @@
         <v>1</v>
       </c>
       <c r="BD8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="BF8" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
         <v>0</v>
@@ -14187,16 +13740,16 @@
         <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
         <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
         <v>0</v>
@@ -14205,7 +13758,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rotherham United - Wycombe Wanderers 1:1</t>
+          <t>Plymouth Argyle - Wycombe Wanderers 1:1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -14213,24 +13766,22 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2025-11-29</t>
-        </is>
+      <c r="C9" s="2" t="n">
+        <v>46020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RCB, RCB3</t>
+          <t>RCB</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="F9" t="n">
-        <v>96</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -14248,73 +13799,73 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>8</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6</v>
+      </c>
+      <c r="W9" t="n">
         <v>4</v>
       </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>17</v>
-      </c>
-      <c r="V9" t="n">
-        <v>10</v>
-      </c>
-      <c r="W9" t="n">
-        <v>9</v>
-      </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="AC9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
@@ -14323,13 +13874,13 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -14353,7 +13904,7 @@
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -14368,10 +13919,10 @@
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
@@ -14380,19 +13931,19 @@
         <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="BG9" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="BH9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
         <v>0</v>
@@ -14413,16 +13964,16 @@
         <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
         <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT9" t="n">
         <v>0</v>
@@ -14431,7 +13982,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers - Lincoln City 3:2</t>
+          <t>Wycombe Wanderers - Bolton Wanderers 2:1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -14439,24 +13990,20 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CB</t>
-        </is>
+      <c r="C10" s="2" t="n">
+        <v>46011</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -14474,13 +14021,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -14498,28 +14045,28 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
         <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -14537,10 +14084,10 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -14549,7 +14096,7 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
@@ -14579,7 +14126,7 @@
         <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
@@ -14594,7 +14141,7 @@
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>0</v>
@@ -14606,19 +14153,19 @@
         <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
       </c>
       <c r="BH10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
         <v>0</v>
@@ -14639,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
         <v>0</v>
@@ -14657,32 +14204,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gillingham - Wycombe Wanderers 0:3</t>
+          <t>Wycombe Wanderers - Plymouth Argyle 0:1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>England. EFL Vertu Trophy</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
+          <t>England. League One</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>46000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>RCB</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="G11" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -14691,28 +14236,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="N11" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="O11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -14724,31 +14269,31 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA11" t="n">
         <v>6</v>
       </c>
-      <c r="Z11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>7</v>
-      </c>
       <c r="AB11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -14757,16 +14302,16 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
@@ -14790,13 +14335,13 @@
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
         <v>0</v>
@@ -14805,7 +14350,7 @@
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
@@ -14820,10 +14365,10 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BB11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
@@ -14832,19 +14377,19 @@
         <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BF11" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="BG11" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="BH11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BI11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="BJ11" t="n">
         <v>0</v>
@@ -14865,10 +14410,10 @@
         <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BR11" t="n">
         <v>0</v>
@@ -14883,32 +14428,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers - Fulham 1:1 (E)</t>
+          <t>Northampton Town - Wycombe Wanderers 2:0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>England. Carabao Cup</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2025-10-28</t>
-        </is>
+          <t>England. EFL Vertu Trophy</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>45993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RCB</t>
+          <t>CB, LCB, RCB</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F12" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14917,31 +14460,31 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="M12" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="N12" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -14950,28 +14493,28 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
+        <v>15</v>
+      </c>
+      <c r="V12" t="n">
         <v>13</v>
       </c>
-      <c r="V12" t="n">
-        <v>5</v>
-      </c>
       <c r="W12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z12" t="n">
         <v>10</v>
       </c>
       <c r="AA12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AC12" t="n">
         <v>2</v>
@@ -14983,16 +14526,16 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG12" t="n">
         <v>4</v>
       </c>
-      <c r="AG12" t="n">
-        <v>2</v>
-      </c>
       <c r="AH12" t="n">
         <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
@@ -15004,7 +14547,7 @@
         <v>3</v>
       </c>
       <c r="AM12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -15016,13 +14559,13 @@
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT12" t="n">
         <v>0</v>
@@ -15031,7 +14574,7 @@
         <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
@@ -15046,31 +14589,31 @@
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE12" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="BF12" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="BG12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="BH12" t="n">
         <v>3</v>
       </c>
       <c r="BI12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ12" t="n">
         <v>0</v>
@@ -15091,16 +14634,16 @@
         <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT12" t="n">
         <v>0</v>
@@ -15109,7 +14652,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers - Huddersfield Town 3:0</t>
+          <t>Rotherham United - Wycombe Wanderers 1:1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -15117,24 +14660,22 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2025-10-25</t>
-        </is>
+      <c r="C13" s="2" t="n">
+        <v>45990</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>RCB</t>
+          <t>RCB, RCB3</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="F13" t="n">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="G13" t="n">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -15143,31 +14684,31 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="N13" t="n">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -15176,128 +14717,128 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="V13" t="n">
         <v>10</v>
       </c>
       <c r="W13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X13" t="n">
         <v>6</v>
       </c>
       <c r="Y13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>53</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH13" t="n">
         <v>6</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="BI13" t="n">
         <v>6</v>
       </c>
-      <c r="AA13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>87</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>36</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>33</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>4</v>
-      </c>
       <c r="BJ13" t="n">
         <v>0</v>
       </c>
@@ -15317,10 +14858,10 @@
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BR13" t="n">
         <v>0</v>
@@ -15335,7 +14876,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Blackpool - Wycombe Wanderers 1:1</t>
+          <t>Wycombe Wanderers - Lincoln City 3:2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -15343,24 +14884,22 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2025-10-18</t>
-        </is>
+      <c r="C14" s="2" t="n">
+        <v>45983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>RCB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="F14" t="n">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -15378,151 +14917,151 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
         <v>4</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>10</v>
-      </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
         <v>3</v>
       </c>
-      <c r="AA14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>26</v>
-      </c>
       <c r="BF14" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="BG14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ14" t="n">
         <v>0</v>
@@ -15543,10 +15082,10 @@
         <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR14" t="n">
         <v>0</v>
@@ -15561,174 +15100,172 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Wigan Athletic - Wycombe Wanderers 0:1</t>
+          <t>Gillingham - Wycombe Wanderers 0:3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>England. League One</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2025-10-11</t>
-        </is>
+          <t>England. EFL Vertu Trophy</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>45972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>RCB</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="G15" t="n">
+        <v>81</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M15" t="n">
+        <v>81</v>
+      </c>
+      <c r="N15" t="n">
+        <v>67</v>
+      </c>
+      <c r="O15" t="n">
+        <v>7</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>16</v>
+      </c>
+      <c r="V15" t="n">
+        <v>12</v>
+      </c>
+      <c r="W15" t="n">
         <v>11</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="X15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA15" t="n">
         <v>7</v>
       </c>
-      <c r="N15" t="n">
-        <v>5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>11</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6</v>
-      </c>
-      <c r="W15" t="n">
+      <c r="AB15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB15" t="n">
         <v>3</v>
       </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1</v>
-      </c>
       <c r="BC15" t="n">
         <v>0</v>
       </c>
@@ -15736,19 +15273,19 @@
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="BF15" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="BG15" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="BH15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="BI15" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="BJ15" t="n">
         <v>0</v>
@@ -15769,10 +15306,10 @@
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BR15" t="n">
         <v>0</v>
@@ -15787,32 +15324,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers - Barnsley 2:2</t>
+          <t>Wycombe Wanderers - Fulham 1:1 (E)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>England. League One</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2025-10-04</t>
-        </is>
+          <t>England. Carabao Cup</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>45958</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RCB</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F16" t="n">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="G16" t="n">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -15821,64 +15356,64 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="N16" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>13</v>
+      </c>
+      <c r="V16" t="n">
         <v>5</v>
       </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
+        <v>5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z16" t="n">
         <v>10</v>
-      </c>
-      <c r="V16" t="n">
-        <v>8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>6</v>
-      </c>
-      <c r="X16" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>15</v>
       </c>
       <c r="AA16" t="n">
         <v>7</v>
       </c>
       <c r="AB16" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -15887,13 +15422,13 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -15905,10 +15440,10 @@
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
@@ -15923,16 +15458,16 @@
         <v>3</v>
       </c>
       <c r="AR16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -15950,31 +15485,31 @@
         <v>0</v>
       </c>
       <c r="BA16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
         <v>6</v>
       </c>
-      <c r="BB16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>38</v>
-      </c>
       <c r="BF16" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="BG16" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="BH16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BI16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BJ16" t="n">
         <v>0</v>
@@ -15995,10 +15530,10 @@
         <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BR16" t="n">
         <v>0</v>
@@ -16013,7 +15548,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AFC Wimbledon - Wycombe Wanderers 2:1</t>
+          <t>Wycombe Wanderers - Huddersfield Town 3:0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -16021,24 +15556,22 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2025-09-27</t>
-        </is>
+      <c r="C17" s="2" t="n">
+        <v>45955</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RCB</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F17" t="n">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="G17" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -16047,31 +15580,31 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="N17" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -16080,32 +15613,32 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="V17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="X17" t="n">
         <v>6</v>
       </c>
       <c r="Y17" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC17" t="n">
         <v>3</v>
       </c>
-      <c r="Z17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2</v>
-      </c>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
@@ -16113,43 +15646,43 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>3</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>2</v>
-      </c>
       <c r="AR17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS17" t="n">
         <v>1</v>
@@ -16161,7 +15694,7 @@
         <v>1</v>
       </c>
       <c r="AV17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
         <v>0</v>
@@ -16176,31 +15709,31 @@
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="BB17" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE17" t="n">
         <v>87</v>
       </c>
       <c r="BF17" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BG17" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="BH17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BI17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ17" t="n">
         <v>0</v>
@@ -16221,10 +15754,10 @@
         <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR17" t="n">
         <v>0</v>
@@ -16239,7 +15772,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers - Northampton Town 2:0</t>
+          <t>Blackpool - Wycombe Wanderers 1:1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -16247,24 +15780,22 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2025-09-20</t>
-        </is>
+      <c r="C18" s="2" t="n">
+        <v>45948</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CB, RCB</t>
+          <t>RCB</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="F18" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -16282,16 +15813,16 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N18" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -16300,56 +15831,56 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="V18" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH18" t="n">
         <v>6</v>
       </c>
-      <c r="Y18" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
+      <c r="AI18" t="n">
         <v>5</v>
       </c>
-      <c r="AG18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1</v>
-      </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
@@ -16357,10 +15888,10 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AM18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -16369,64 +15900,64 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AR18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
         <v>3</v>
       </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2</v>
-      </c>
       <c r="BB18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE18" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BF18" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BG18" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="BH18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
         <v>0</v>
@@ -16447,10 +15978,10 @@
         <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR18" t="n">
         <v>0</v>
@@ -16465,7 +15996,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Peterborough United - Wycombe Wanderers 2:1</t>
+          <t>Wigan Athletic - Wycombe Wanderers 0:1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -16473,24 +16004,22 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2025-09-13</t>
-        </is>
+      <c r="C19" s="2" t="n">
+        <v>45941</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>RCB</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="F19" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G19" t="n">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -16499,19 +16028,19 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -16532,31 +16061,31 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
+        <v>3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z19" t="n">
         <v>4</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5</v>
       </c>
       <c r="AA19" t="n">
         <v>3</v>
       </c>
       <c r="AB19" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -16565,10 +16094,10 @@
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
@@ -16583,70 +16112,70 @@
         <v>0</v>
       </c>
       <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF19" t="n">
         <v>4</v>
       </c>
-      <c r="AM19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>13</v>
-      </c>
       <c r="BG19" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="BH19" t="n">
         <v>1</v>
@@ -16673,10 +16202,10 @@
         <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR19" t="n">
         <v>0</v>
@@ -16691,7 +16220,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers - Mansfield Town 2:0</t>
+          <t>Wycombe Wanderers - Barnsley 2:2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -16699,24 +16228,22 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2025-09-06</t>
-        </is>
+      <c r="C20" s="2" t="n">
+        <v>45934</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CB, RCB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F20" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="G20" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -16725,184 +16252,184 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="M20" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="N20" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="O20" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>10</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>6</v>
+      </c>
+      <c r="X20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>3</v>
       </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="AR20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH20" t="n">
         <v>7</v>
       </c>
-      <c r="V20" t="n">
-        <v>4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z20" t="n">
+      <c r="BI20" t="n">
         <v>6</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="BJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
         <v>5</v>
       </c>
-      <c r="AB20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>14</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>2</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>2</v>
-      </c>
       <c r="BQ20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BR20" t="n">
         <v>0</v>
@@ -16917,7 +16444,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Stevenage - Wycombe Wanderers 1:0</t>
+          <t>AFC Wimbledon - Wycombe Wanderers 2:1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -16925,24 +16452,22 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
+      <c r="C21" s="2" t="n">
+        <v>45927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CB, RCB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F21" t="n">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="G21" t="n">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -16960,22 +16485,22 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="N21" t="n">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -16984,28 +16509,28 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="V21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X21" t="n">
         <v>6</v>
       </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA21" t="n">
         <v>8</v>
       </c>
-      <c r="AA21" t="n">
-        <v>6</v>
-      </c>
       <c r="AB21" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AC21" t="n">
         <v>2</v>
@@ -17017,16 +16542,16 @@
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
@@ -17035,10 +16560,10 @@
         <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
@@ -17047,13 +16572,13 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS21" t="n">
         <v>1</v>
@@ -17065,7 +16590,7 @@
         <v>1</v>
       </c>
       <c r="AV21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW21" t="n">
         <v>0</v>
@@ -17074,37 +16599,37 @@
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
         <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BC21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="BF21" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="BG21" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="BH21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BI21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ21" t="n">
         <v>0</v>
@@ -17134,7 +16659,7 @@
         <v>0</v>
       </c>
       <c r="BS21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BT21" t="n">
         <v>0</v>
@@ -17143,7 +16668,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers - Reading 2:2</t>
+          <t>Wycombe Wanderers - Northampton Town 2:0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -17151,24 +16676,22 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2025-08-23</t>
-        </is>
+      <c r="C22" s="2" t="n">
+        <v>45920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>RCB</t>
+          <t>CB, RCB</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F22" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="G22" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -17177,25 +16700,25 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="N22" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -17204,46 +16727,46 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W22" t="n">
+        <v>7</v>
+      </c>
+      <c r="X22" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z22" t="n">
         <v>10</v>
       </c>
-      <c r="X22" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
         <v>5</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>4</v>
       </c>
       <c r="AG22" t="n">
         <v>4</v>
@@ -17261,10 +16784,10 @@
         <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
@@ -17276,22 +16799,22 @@
         <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="n">
         <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW22" t="n">
         <v>0</v>
@@ -17306,10 +16829,10 @@
         <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC22" t="n">
         <v>0</v>
@@ -17318,19 +16841,19 @@
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="BF22" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BG22" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="BH22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BI22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BJ22" t="n">
         <v>0</v>
@@ -17351,16 +16874,16 @@
         <v>0</v>
       </c>
       <c r="BP22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BR22" t="n">
         <v>0</v>
       </c>
       <c r="BS22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BT22" t="n">
         <v>0</v>
@@ -17369,7 +16892,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers - Exeter City 0:1</t>
+          <t>Peterborough United - Wycombe Wanderers 2:1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -17377,24 +16900,22 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2025-08-19</t>
-        </is>
+      <c r="C23" s="2" t="n">
+        <v>45913</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>RCB</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F23" t="n">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="G23" t="n">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -17403,160 +16924,160 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="M23" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="N23" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>9</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>4</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y23" t="n">
         <v>6</v>
       </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>10</v>
-      </c>
-      <c r="V23" t="n">
-        <v>10</v>
-      </c>
-      <c r="W23" t="n">
-        <v>6</v>
-      </c>
-      <c r="X23" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="Z23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
         <v>4</v>
       </c>
-      <c r="Z23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AM23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF23" t="n">
         <v>13</v>
       </c>
-      <c r="AC23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>74</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>27</v>
-      </c>
       <c r="BG23" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="BH23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BI23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ23" t="n">
         <v>0</v>
@@ -17577,16 +17098,16 @@
         <v>0</v>
       </c>
       <c r="BP23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR23" t="n">
         <v>0</v>
       </c>
       <c r="BS23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT23" t="n">
         <v>0</v>
@@ -17595,7 +17116,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers - Stockport County 1:2</t>
+          <t>Wycombe Wanderers - Mansfield Town 2:0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -17603,24 +17124,22 @@
           <t>England. League One</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2025-08-09</t>
-        </is>
+      <c r="C24" s="2" t="n">
+        <v>45906</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>RCB</t>
+          <t>CB, RCB</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F24" t="n">
-        <v>110</v>
+        <v>49</v>
       </c>
       <c r="G24" t="n">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -17629,25 +17148,25 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="N24" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -17662,40 +17181,40 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="V24" t="n">
+        <v>4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z24" t="n">
         <v>6</v>
       </c>
-      <c r="W24" t="n">
-        <v>9</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="AA24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC24" t="n">
         <v>4</v>
       </c>
-      <c r="Y24" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1</v>
-      </c>
       <c r="AD24" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG24" t="n">
         <v>1</v>
@@ -17704,7 +17223,7 @@
         <v>4</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ24" t="n">
         <v>0</v>
@@ -17713,13 +17232,13 @@
         <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AM24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -17728,22 +17247,22 @@
         <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
         <v>0</v>
@@ -17761,7 +17280,7 @@
         <v>3</v>
       </c>
       <c r="BB24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC24" t="n">
         <v>0</v>
@@ -17770,51 +17289,947 @@
         <v>0</v>
       </c>
       <c r="BE24" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Stevenage - Wycombe Wanderers 1:0</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>England. League One</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CB, RCB</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103</v>
+      </c>
+      <c r="F25" t="n">
+        <v>73</v>
+      </c>
+      <c r="G25" t="n">
+        <v>58</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>48</v>
+      </c>
+      <c r="N25" t="n">
+        <v>46</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>18</v>
+      </c>
+      <c r="V25" t="n">
+        <v>10</v>
+      </c>
+      <c r="W25" t="n">
+        <v>10</v>
+      </c>
+      <c r="X25" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Wycombe Wanderers - Reading 2:2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>England. League One</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>45892</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>97</v>
+      </c>
+      <c r="F26" t="n">
+        <v>85</v>
+      </c>
+      <c r="G26" t="n">
+        <v>72</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M26" t="n">
+        <v>60</v>
+      </c>
+      <c r="N26" t="n">
+        <v>59</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>16</v>
+      </c>
+      <c r="V26" t="n">
+        <v>12</v>
+      </c>
+      <c r="W26" t="n">
+        <v>10</v>
+      </c>
+      <c r="X26" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Wycombe Wanderers - Exeter City 0:1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>England. League One</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>45888</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>99</v>
+      </c>
+      <c r="F27" t="n">
+        <v>113</v>
+      </c>
+      <c r="G27" t="n">
+        <v>101</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>97</v>
+      </c>
+      <c r="N27" t="n">
+        <v>90</v>
+      </c>
+      <c r="O27" t="n">
+        <v>6</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>10</v>
+      </c>
+      <c r="V27" t="n">
+        <v>10</v>
+      </c>
+      <c r="W27" t="n">
+        <v>6</v>
+      </c>
+      <c r="X27" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>74</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Wycombe Wanderers - Stockport County 1:2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>England. League One</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>45878</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>RCB</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103</v>
+      </c>
+      <c r="F28" t="n">
+        <v>110</v>
+      </c>
+      <c r="G28" t="n">
+        <v>88</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88</v>
+      </c>
+      <c r="N28" t="n">
+        <v>82</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>16</v>
+      </c>
+      <c r="V28" t="n">
+        <v>6</v>
+      </c>
+      <c r="W28" t="n">
+        <v>9</v>
+      </c>
+      <c r="X28" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
         <v>70</v>
       </c>
-      <c r="BF24" t="n">
+      <c r="BF28" t="n">
         <v>19</v>
       </c>
-      <c r="BG24" t="n">
+      <c r="BG28" t="n">
         <v>13</v>
       </c>
-      <c r="BH24" t="n">
-        <v>2</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT24" t="n">
+      <c r="BH28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18454,89 +18869,12 @@
       <c r="AA2" t="n">
         <v>4</v>
       </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
         <v>4</v>
       </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
         <v>18</v>
       </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
-      <c r="BW2" t="inlineStr"/>
-      <c r="BX2" t="inlineStr"/>
-      <c r="BY2" t="inlineStr"/>
-      <c r="BZ2" t="inlineStr"/>
-      <c r="CA2" t="inlineStr"/>
-      <c r="CB2" t="inlineStr"/>
-      <c r="CC2" t="inlineStr"/>
-      <c r="CD2" t="inlineStr"/>
-      <c r="CE2" t="inlineStr"/>
-      <c r="CF2" t="inlineStr"/>
-      <c r="CG2" t="inlineStr"/>
-      <c r="CH2" t="inlineStr"/>
-      <c r="CI2" t="inlineStr"/>
-      <c r="CJ2" t="inlineStr"/>
-      <c r="CK2" t="inlineStr"/>
-      <c r="CL2" t="inlineStr"/>
-      <c r="CM2" t="inlineStr"/>
-      <c r="CN2" t="inlineStr"/>
-      <c r="CO2" t="inlineStr"/>
-      <c r="CP2" t="inlineStr"/>
-      <c r="CQ2" t="inlineStr"/>
-      <c r="CR2" t="inlineStr"/>
-      <c r="CS2" t="inlineStr"/>
-      <c r="CT2" t="inlineStr"/>
-      <c r="CU2" t="inlineStr"/>
-      <c r="CV2" t="inlineStr"/>
-      <c r="CW2" t="inlineStr"/>
-      <c r="CX2" t="inlineStr"/>
-      <c r="CY2" t="inlineStr"/>
-      <c r="CZ2" t="inlineStr"/>
-      <c r="DA2" t="inlineStr"/>
-      <c r="DB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18628,89 +18966,12 @@
       <c r="AA3" t="n">
         <v>2</v>
       </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
         <v>18</v>
       </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr"/>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr"/>
-      <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="inlineStr"/>
-      <c r="CC3" t="inlineStr"/>
-      <c r="CD3" t="inlineStr"/>
-      <c r="CE3" t="inlineStr"/>
-      <c r="CF3" t="inlineStr"/>
-      <c r="CG3" t="inlineStr"/>
-      <c r="CH3" t="inlineStr"/>
-      <c r="CI3" t="inlineStr"/>
-      <c r="CJ3" t="inlineStr"/>
-      <c r="CK3" t="inlineStr"/>
-      <c r="CL3" t="inlineStr"/>
-      <c r="CM3" t="inlineStr"/>
-      <c r="CN3" t="inlineStr"/>
-      <c r="CO3" t="inlineStr"/>
-      <c r="CP3" t="inlineStr"/>
-      <c r="CQ3" t="inlineStr"/>
-      <c r="CR3" t="inlineStr"/>
-      <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="inlineStr"/>
-      <c r="CU3" t="inlineStr"/>
-      <c r="CV3" t="inlineStr"/>
-      <c r="CW3" t="inlineStr"/>
-      <c r="CX3" t="inlineStr"/>
-      <c r="CY3" t="inlineStr"/>
-      <c r="CZ3" t="inlineStr"/>
-      <c r="DA3" t="inlineStr"/>
-      <c r="DB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18802,89 +19063,12 @@
       <c r="AA4" t="n">
         <v>3</v>
       </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
         <v>7</v>
       </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
-      <c r="BW4" t="inlineStr"/>
-      <c r="BX4" t="inlineStr"/>
-      <c r="BY4" t="inlineStr"/>
-      <c r="BZ4" t="inlineStr"/>
-      <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="inlineStr"/>
-      <c r="CC4" t="inlineStr"/>
-      <c r="CD4" t="inlineStr"/>
-      <c r="CE4" t="inlineStr"/>
-      <c r="CF4" t="inlineStr"/>
-      <c r="CG4" t="inlineStr"/>
-      <c r="CH4" t="inlineStr"/>
-      <c r="CI4" t="inlineStr"/>
-      <c r="CJ4" t="inlineStr"/>
-      <c r="CK4" t="inlineStr"/>
-      <c r="CL4" t="inlineStr"/>
-      <c r="CM4" t="inlineStr"/>
-      <c r="CN4" t="inlineStr"/>
-      <c r="CO4" t="inlineStr"/>
-      <c r="CP4" t="inlineStr"/>
-      <c r="CQ4" t="inlineStr"/>
-      <c r="CR4" t="inlineStr"/>
-      <c r="CS4" t="inlineStr"/>
-      <c r="CT4" t="inlineStr"/>
-      <c r="CU4" t="inlineStr"/>
-      <c r="CV4" t="inlineStr"/>
-      <c r="CW4" t="inlineStr"/>
-      <c r="CX4" t="inlineStr"/>
-      <c r="CY4" t="inlineStr"/>
-      <c r="CZ4" t="inlineStr"/>
-      <c r="DA4" t="inlineStr"/>
-      <c r="DB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18976,89 +19160,12 @@
       <c r="AA5" t="n">
         <v>1</v>
       </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
         <v>1</v>
       </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
         <v>1</v>
       </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
-      <c r="BW5" t="inlineStr"/>
-      <c r="BX5" t="inlineStr"/>
-      <c r="BY5" t="inlineStr"/>
-      <c r="BZ5" t="inlineStr"/>
-      <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="inlineStr"/>
-      <c r="CC5" t="inlineStr"/>
-      <c r="CD5" t="inlineStr"/>
-      <c r="CE5" t="inlineStr"/>
-      <c r="CF5" t="inlineStr"/>
-      <c r="CG5" t="inlineStr"/>
-      <c r="CH5" t="inlineStr"/>
-      <c r="CI5" t="inlineStr"/>
-      <c r="CJ5" t="inlineStr"/>
-      <c r="CK5" t="inlineStr"/>
-      <c r="CL5" t="inlineStr"/>
-      <c r="CM5" t="inlineStr"/>
-      <c r="CN5" t="inlineStr"/>
-      <c r="CO5" t="inlineStr"/>
-      <c r="CP5" t="inlineStr"/>
-      <c r="CQ5" t="inlineStr"/>
-      <c r="CR5" t="inlineStr"/>
-      <c r="CS5" t="inlineStr"/>
-      <c r="CT5" t="inlineStr"/>
-      <c r="CU5" t="inlineStr"/>
-      <c r="CV5" t="inlineStr"/>
-      <c r="CW5" t="inlineStr"/>
-      <c r="CX5" t="inlineStr"/>
-      <c r="CY5" t="inlineStr"/>
-      <c r="CZ5" t="inlineStr"/>
-      <c r="DA5" t="inlineStr"/>
-      <c r="DB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19150,18 +19257,12 @@
       <c r="AA6" t="n">
         <v>0</v>
       </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
         <v>1</v>
       </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>Wycombe Wanderers - Wigan Athletic 2:0</t>
@@ -19470,18 +19571,12 @@
       <c r="AA7" t="n">
         <v>0</v>
       </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
         <v>4</v>
       </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>Northampton Town - Wycombe Wanderers 1:2</t>
@@ -19792,18 +19887,12 @@
       <c r="AA8" t="n">
         <v>0</v>
       </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="n">
         <v>7</v>
       </c>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>Wycombe Wanderers - AFC Wimbledon 2:0</t>
@@ -20114,18 +20203,12 @@
       <c r="AA9" t="n">
         <v>0</v>
       </c>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
         <v>6</v>
       </c>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr">
         <is>
           <t>Plymouth Argyle - Wycombe Wanderers 1:1</t>
@@ -20415,8 +20498,6 @@
       <c r="T10" t="n">
         <v>2</v>
       </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
         <v>8</v>
       </c>
@@ -20432,18 +20513,12 @@
       <c r="AA10" t="n">
         <v>0</v>
       </c>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
         <v>1</v>
       </c>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr">
         <is>
           <t>Wycombe Wanderers - Bolton Wanderers 2:1</t>
@@ -20752,18 +20827,12 @@
       <c r="AA11" t="n">
         <v>0</v>
       </c>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="n">
         <v>11</v>
       </c>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>Wycombe Wanderers - Plymouth Argyle 0:1</t>
@@ -20985,45 +21054,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>Northampton Town - Wycombe Wanderers 2:0</t>
@@ -21277,37 +21312,12 @@
       <c r="H13" t="n">
         <v>1211</v>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>Rotherham United - Wycombe Wanderers 1:1</t>
@@ -21618,18 +21628,12 @@
       <c r="AA14" t="n">
         <v>0</v>
       </c>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="n">
         <v>4</v>
       </c>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr">
         <is>
           <t>Wycombe Wanderers - Lincoln City 3:2</t>
@@ -21851,45 +21855,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>2025-11-11</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr">
         <is>
           <t>Gillingham - Wycombe Wanderers 0:3</t>
@@ -22111,45 +22081,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr">
         <is>
           <t>Wycombe Wanderers - Fulham 1:1 (E)</t>
@@ -22460,18 +22396,12 @@
       <c r="AA17" t="n">
         <v>3</v>
       </c>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="n">
         <v>1</v>
       </c>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="n">
         <v>21</v>
       </c>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr">
         <is>
           <t>Wycombe Wanderers - Huddersfield Town 3:0</t>
@@ -22782,18 +22712,12 @@
       <c r="AA18" t="n">
         <v>0</v>
       </c>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="n">
         <v>0</v>
       </c>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="n">
         <v>7</v>
       </c>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>Blackpool - Wycombe Wanderers 1:1</t>
@@ -23104,18 +23028,12 @@
       <c r="AA19" t="n">
         <v>2</v>
       </c>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="n">
         <v>0</v>
       </c>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="n">
         <v>11</v>
       </c>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>Wigan Athletic - Wycombe Wanderers 0:1</t>
@@ -23426,18 +23344,12 @@
       <c r="AA20" t="n">
         <v>6</v>
       </c>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="n">
         <v>0</v>
       </c>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="n">
         <v>18</v>
       </c>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>Wycombe Wanderers - Barnsley 2:2</t>
@@ -23748,18 +23660,12 @@
       <c r="AA21" t="n">
         <v>0</v>
       </c>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="n">
         <v>0</v>
       </c>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
         <v>16</v>
       </c>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>AFC Wimbledon - Wycombe Wanderers 2:1</t>
@@ -24070,18 +23976,12 @@
       <c r="AA22" t="n">
         <v>6</v>
       </c>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="n">
         <v>3</v>
       </c>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="n">
         <v>20</v>
       </c>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>Wycombe Wanderers - Northampton Town 2:0</t>
@@ -24392,18 +24292,12 @@
       <c r="AA23" t="n">
         <v>0</v>
       </c>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="n">
         <v>0</v>
       </c>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="n">
         <v>13</v>
       </c>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>Peterborough United - Wycombe Wanderers 2:1</t>
@@ -24714,18 +24608,12 @@
       <c r="AA24" t="n">
         <v>6</v>
       </c>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="n">
         <v>3</v>
       </c>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="n">
         <v>21</v>
       </c>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr">
         <is>
           <t>Wycombe Wanderers - Mansfield Town 2:0</t>
@@ -25036,18 +24924,12 @@
       <c r="AA25" t="n">
         <v>3</v>
       </c>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="n">
         <v>0</v>
       </c>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="n">
         <v>15</v>
       </c>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr">
         <is>
           <t>Stevenage - Wycombe Wanderers 1:0</t>
@@ -25358,18 +25240,12 @@
       <c r="AA26" t="n">
         <v>2</v>
       </c>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="n">
         <v>0</v>
       </c>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="n">
         <v>15</v>
       </c>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr">
         <is>
           <t>Wycombe Wanderers - Reading 2:2</t>
@@ -25680,18 +25556,12 @@
       <c r="AA27" t="n">
         <v>1</v>
       </c>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="n">
         <v>1</v>
       </c>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="n">
         <v>10</v>
       </c>
-      <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr">
         <is>
           <t>Wycombe Wanderers - Exeter City 0:1</t>
@@ -26002,18 +25872,12 @@
       <c r="AA28" t="n">
         <v>1</v>
       </c>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="n">
         <v>0</v>
       </c>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="n">
         <v>14</v>
       </c>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr">
         <is>
           <t>Wycombe Wanderers - Stockport County 1:2</t>
